--- a/data/resultados_experimento.xlsx
+++ b/data/resultados_experimento.xlsx
@@ -589,35 +589,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-06-25T06:38:38.483281</t>
+          <t>2025-06-29T21:31:27.695655</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.05946581659882213</v>
+        <v>0.0642716523001127</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001860439990734883</v>
+        <v>0.002986806940023528</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05827353199856589</v>
+        <v>0.05936170800032414</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06438373799755936</v>
+        <v>0.06844271099998878</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05877141199744074</v>
+        <v>0.06470139950010889</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05867352774839674</v>
+        <v>0.06296408149989929</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05909573875032947</v>
+        <v>0.06580232025009991</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05813493800327305</v>
+        <v>0.06213501932871297</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06079669519437121</v>
+        <v>0.06640828527151243</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -632,20 +632,20 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>168303.452328378</v>
+        <v>155896.6117900158</v>
       </c>
       <c r="S2" t="n">
-        <v>4959.7539915788</v>
+        <v>7348.646558730344</v>
       </c>
       <c r="T2" t="n">
-        <v>155318.7235009418</v>
+        <v>146107.5964685508</v>
       </c>
       <c r="U2" t="n">
-        <v>171604.4944769454</v>
+        <v>168458.7646963493</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>[0.05830308700387832, 0.05875803999515483, 0.05892295599915087, 0.05867070199747104, 0.05868200500117382, 0.06072598899481818, 0.05915333300072234, 0.05878478399972664, 0.06438373799755936, 0.058273531998565886]</t>
+          <t>[0.06287675299972761, 0.06603549300007217, 0.06510280200018315, 0.06322606700041433, 0.06844271099998878, 0.06452724300015689, 0.068101150000075, 0.06016704000012396, 0.0648755560000609, 0.05936170800032414]</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>[171517.504713512, 170189.47536072673, 169713.14202471628, 170442.82170734965, 170409.99195238762, 164674.13977981175, 169052.18172368896, 170112.04804369956, 155318.72350094176, 171604.4944769454]</t>
+          <t>[159041.29146177953, 151433.71459328805, 153603.21971966533, 158162.61352986685, 146107.59646855076, 154973.30329107176, 146840.3984365754, 166203.95485600416, 154141.26084700704, 168458.7646963493]</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -694,35 +694,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-06-25T06:38:39.919628</t>
+          <t>2025-06-29T21:31:29.215455</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.04849277650064323</v>
+        <v>0.05179314290003276</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001860429118280827</v>
+        <v>0.006735991211896062</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04693179200694431</v>
+        <v>0.04704201300000932</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05305616799887503</v>
+        <v>0.06835226499970304</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04788758949871408</v>
+        <v>0.04897329549999085</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04740723425129545</v>
+        <v>0.04739303075018597</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04849251724954229</v>
+        <v>0.05445494474997759</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04716190568277924</v>
+        <v>0.04697450506792615</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04982364731850722</v>
+        <v>0.05661178073213938</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -737,20 +737,20 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>206474.4225520033</v>
+        <v>195585.1689254989</v>
       </c>
       <c r="S3" t="n">
-        <v>7480.507757924442</v>
+        <v>21577.58799858037</v>
       </c>
       <c r="T3" t="n">
-        <v>188479.4996919497</v>
+        <v>146300.9309207741</v>
       </c>
       <c r="U3" t="n">
-        <v>213075.1793692502</v>
+        <v>212575.9371733947</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>[0.0479675419992418, 0.04716456599999219, 0.046931792006944306, 0.04783396400307538, 0.04790342100022826, 0.05026605400053086, 0.04866750899964245, 0.04787175799719989, 0.04726499100070214, 0.053056167998875026]</t>
+          <t>[0.04704201300000932, 0.047657956999955786, 0.04712196300033611, 0.0473047220002627, 0.0479407729999366, 0.05075450699996509, 0.05000581800004511, 0.05568842399998175, 0.06835226499970304, 0.056062987000132125]</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>[208474.30539922317, 212023.57719143765, 213075.17936925017, 209056.47709558572, 208753.3581359951, 198941.41680376165, 205475.89563446667, 208891.4303206688, 211573.08587769425, 188479.49969194975]</t>
+          <t>[212575.93717339475, 209828.54972170288, 212215.26785564245, 211395.38670039043, 208590.71254468977, 197026.8374394195, 199976.73070743447, 179570.5333662033, 146300.93092077412, 178370.802825337]</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>1.226281951457932</v>
+        <v>1.240929758291846</v>
       </c>
     </row>
     <row r="4">
@@ -799,35 +799,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-06-25T06:38:41.413969</t>
+          <t>2025-06-29T21:31:30.827376</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05688670610106783</v>
+        <v>0.059959496700003</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002615851715837612</v>
+        <v>0.00661040440914978</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05505975699634291</v>
+        <v>0.05535168899996279</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06221978700341424</v>
+        <v>0.07585036599994055</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05554619300164632</v>
+        <v>0.05655928400005905</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05525108775145782</v>
+        <v>0.05560156425008245</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05756724325328832</v>
+        <v>0.06130843375001405</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05501543851110195</v>
+        <v>0.05523069825454193</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05875797369103371</v>
+        <v>0.06468829514546406</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -842,20 +842,20 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>176106.2972875453</v>
+        <v>168379.1153065919</v>
       </c>
       <c r="S4" t="n">
-        <v>7693.719577874511</v>
+        <v>16195.69289689577</v>
       </c>
       <c r="T4" t="n">
-        <v>160720.5759070062</v>
+        <v>131838.5200673631</v>
       </c>
       <c r="U4" t="n">
-        <v>181620.8524251969</v>
+        <v>180662.9604384199</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>[0.055914750999363605, 0.05505975699634291, 0.05536678800126538, 0.058118074004596565, 0.06080419399950188, 0.055212521001521964, 0.06221978700341424, 0.05507880300137913, 0.05544265400385484, 0.05564973199943779]</t>
+          <t>[0.06588900199994896, 0.07585036599994055, 0.061285035999844695, 0.0613162330000705, 0.05704139799991026, 0.05535168899996279, 0.05607717000020784, 0.05556135799997719, 0.05550053199976901, 0.05572218300039822]</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>[178843.68295074435, 181620.85242519694, 180613.6920886842, 172063.51330928653, 164462.33955641155, 181118.3372649176, 160720.57590700625, 181558.0487424465, 180366.54593239198, 179695.38469836704]</t>
+          <t>[151770.39712952013, 131838.52006736313, 163171.96909250965, 163088.94905511403, 175311.27129836005, 180662.96043841992, 178325.68940199615, 179981.20204340768, 180178.45306494753, 179461.74147428028]</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -904,35 +904,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-06-25T06:38:42.941213</t>
+          <t>2025-06-29T21:31:32.306718</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05737408799905097</v>
+        <v>0.05541215320008632</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003278322904571118</v>
+        <v>0.0008975726045036777</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05513511999743059</v>
+        <v>0.0548527680002735</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06597674200020265</v>
+        <v>0.05792404800013173</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05641957150146482</v>
+        <v>0.05517874600013783</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05530199624809029</v>
+        <v>0.05503808524974829</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05794338024861645</v>
+        <v>0.0552928245002704</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05502891706920627</v>
+        <v>0.05477006843882867</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05971925892889567</v>
+        <v>0.05605423796134397</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -947,20 +947,20 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>174759.4558026731</v>
+        <v>180506.877359197</v>
       </c>
       <c r="S5" t="n">
-        <v>9049.990222135866</v>
+        <v>2816.038377731491</v>
       </c>
       <c r="T5" t="n">
-        <v>151568.5633578161</v>
+        <v>172639.8679867342</v>
       </c>
       <c r="U5" t="n">
-        <v>181372.5988166167</v>
+        <v>182306.2055856532</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>[0.05595914000150515, 0.0586403689958388, 0.056975457999214996, 0.06597674200020265, 0.056880003001424484, 0.058266020998416934, 0.05525418699835427, 0.05544542399729835, 0.05520841600082349, 0.05513511999743059]</t>
+          <t>[0.054921275000197056, 0.0548527680002735, 0.055197532999955, 0.055300392000390275, 0.05515995900032067, 0.05500521599969943, 0.057924048000131734, 0.05527012199991077, 0.055136692999894876, 0.055353526000089914]</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>[178701.8170710098, 170530.98695046775, 175514.16611934526, 151568.56335781608, 175808.71083550336, 171626.61579845476, 180981.7598130228, 180357.53501474284, 181131.80424975132, 181372.5988166167]</t>
+          <t>[182078.80279480256, 182306.2055856532, 181167.51703392528, 180830.54456339887, 181290.92517893034, 181800.94047907463, 172639.86798673423, 180929.58072385192, 181367.4244122524, 180656.96483334695]</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>0.9915051913680754</v>
+        <v>1.082064010100759</v>
       </c>
     </row>
     <row r="6">
@@ -1009,73 +1009,73 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-06-25T06:38:51.264037</t>
+          <t>2025-06-29T21:31:40.955936</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7149365504999878</v>
+        <v>0.7424729585999558</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01313972176666356</v>
+        <v>0.02113974497291606</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6998494830040727</v>
+        <v>0.7046222049998505</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7412023779979791</v>
+        <v>0.7689441210000041</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7134550694972859</v>
+        <v>0.74634063350004</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7049925172486837</v>
+        <v>0.7411172144998091</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7188240324976505</v>
+        <v>0.7519812880001382</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7055369597914397</v>
+        <v>0.7273504960427479</v>
       </c>
       <c r="M6" t="n">
-        <v>0.724336141208536</v>
+        <v>0.7575954211571636</v>
       </c>
       <c r="N6" t="n">
-        <v>1.558984375</v>
+        <v>3.285546875</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7795564326000222</v>
+        <v>0.1964070890495204</v>
       </c>
       <c r="P6" t="n">
-        <v>1.28515625</v>
+        <v>2.7265625</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.765625</v>
+        <v>3.34765625</v>
       </c>
       <c r="R6" t="n">
-        <v>139914.5077523285</v>
+        <v>134785.6581354807</v>
       </c>
       <c r="S6" t="n">
-        <v>2536.838948912026</v>
+        <v>3927.93679459333</v>
       </c>
       <c r="T6" t="n">
-        <v>134915.9190100071</v>
+        <v>130048.4616098645</v>
       </c>
       <c r="U6" t="n">
-        <v>142887.8672178973</v>
+        <v>141920.0236529889</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>[0.7114874539984157, 0.7313902220048476, 0.6998494830040727, 0.7045987829988007, 0.7194652179969125, 0.7061737199983327, 0.7169004759998643, 0.715422684996156, 0.7028750860044966, 0.7412023779979791]</t>
+          <t>[0.7077368860000206, 0.7046222049998505, 0.7469167160002144, 0.7641639669996039, 0.7517529910001031, 0.7408490479997454, 0.7689441210000041, 0.7520573870001499, 0.7419217140000001, 0.7457645509998656]</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>[3.765625, 1.54296875, 1.28515625, 1.28515625, 1.28515625, 1.28515625, 1.28515625, 1.28515625, 1.28515625, 1.28515625]</t>
+          <t>[2.7265625, 3.34765625, 3.34765625, 3.34765625, 3.34765625, 3.34765625, 3.34765625, 3.34765625, 3.34765625, 3.34765625]</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>[140550.61609030518, 136725.91865650783, 142887.8672178973, 141924.74130369056, 138992.12567692067, 141608.2150440774, 139489.3759284084, 139777.5078945635, 142272.79070090735, 134915.91901000708]</t>
+          <t>[141295.44747226455, 141920.02365298892, 133883.73543908112, 130861.96721972869, 133022.41719978245, 134980.2638877581, 130048.46160986446, 132968.5762397545, 134785.11022525484, 134090.57840832934]</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -1114,73 +1114,73 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-06-25T06:39:03.744452</t>
+          <t>2025-06-29T21:31:54.335485</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.125886663700658</v>
+        <v>1.210067964900009</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005601899508837191</v>
+        <v>0.0603754622000333</v>
       </c>
       <c r="G7" t="n">
-        <v>1.119707912002923</v>
+        <v>1.146663179999905</v>
       </c>
       <c r="H7" t="n">
-        <v>1.135155918003875</v>
+        <v>1.33491241999991</v>
       </c>
       <c r="I7" t="n">
-        <v>1.125353981999069</v>
+        <v>1.196193957499872</v>
       </c>
       <c r="J7" t="n">
-        <v>1.120632753252721</v>
+        <v>1.16844721450002</v>
       </c>
       <c r="K7" t="n">
-        <v>1.129864422249739</v>
+        <v>1.225062132000176</v>
       </c>
       <c r="L7" t="n">
-        <v>1.121879306200358</v>
+        <v>1.166877961062977</v>
       </c>
       <c r="M7" t="n">
-        <v>1.129894021200957</v>
+        <v>1.25325796873704</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.063671875</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.2013481478935335</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>0.63671875</v>
       </c>
       <c r="R7" t="n">
-        <v>88820.86248949837</v>
+        <v>82817.52601386004</v>
       </c>
       <c r="S7" t="n">
-        <v>441.229373328749</v>
+        <v>3957.581777393328</v>
       </c>
       <c r="T7" t="n">
-        <v>88093.62521392295</v>
+        <v>74911.28144571969</v>
       </c>
       <c r="U7" t="n">
-        <v>89309.0054361775</v>
+        <v>87209.56750351771</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>[1.1351559180038748, 1.1259120059985435, 1.1204751640034374, 1.1286890979972668, 1.1326117710050312, 1.1211055210005725, 1.1302561970005627, 1.119707912002923, 1.1201570919947699, 1.124795957999595]</t>
+          <t>[1.154461855000136, 1.2284966760003044, 1.3349124199999096, 1.2884339110000838, 1.1999294229999578, 1.214758499999789, 1.1739533590002793, 1.1666118329999335, 1.192458491999787, 1.146663179999905]</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
+          <t>[0.63671875, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>[88093.62521392295, 88816.88752516008, 89247.85056609538, 88598.35731331052, 88291.50690466892, 89197.6697347376, 88475.51578604635, 89309.0054361775, 89273.19276434748, 88905.0136505167]</t>
+          <t>[86620.44533293672, 81400.30164800806, 74911.2814457197, 77613.604505628, 83338.23480216763, 82320.8892961172, 85182.25978343676, 85718.31449956303, 83860.36132150574, 87209.56750351771]</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>0.63499868463676</v>
+        <v>0.6135795510141518</v>
       </c>
     </row>
     <row r="8">
@@ -1219,73 +1219,73 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-06-25T06:39:11.634842</t>
+          <t>2025-06-29T21:32:02.537335</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.6780599705984059</v>
+        <v>0.7039190375000089</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01232589718933624</v>
+        <v>0.01365855955939503</v>
       </c>
       <c r="G8" t="n">
-        <v>0.664658479996433</v>
+        <v>0.6797443229997953</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7069873859945801</v>
+        <v>0.7271815169997353</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6737814385014644</v>
+        <v>0.7050614390000192</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6707823382457718</v>
+        <v>0.6997516280001719</v>
       </c>
       <c r="K8" t="n">
-        <v>0.684062688749691</v>
+        <v>0.7120660575000102</v>
       </c>
       <c r="L8" t="n">
-        <v>0.669242554921512</v>
+        <v>0.6941482925933427</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6868773862752999</v>
+        <v>0.7136897824066752</v>
       </c>
       <c r="N8" t="n">
-        <v>1.28515625</v>
+        <v>2.5484375</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.6482445119440851</v>
       </c>
       <c r="P8" t="n">
-        <v>1.28515625</v>
+        <v>2.31640625</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.28515625</v>
+        <v>4.37890625</v>
       </c>
       <c r="R8" t="n">
-        <v>147522.5147444713</v>
+        <v>142110.1911207669</v>
       </c>
       <c r="S8" t="n">
-        <v>2624.809355217112</v>
+        <v>2772.226822203612</v>
       </c>
       <c r="T8" t="n">
-        <v>141445.2393083667</v>
+        <v>137517.2466052054</v>
       </c>
       <c r="U8" t="n">
-        <v>150453.2071877525</v>
+        <v>147114.1377962345</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>[0.6727143680036534, 0.664658479996433, 0.6704657519949251, 0.7069873859945801, 0.6851861309987726, 0.6806923620024463, 0.6748485089992755, 0.6853952940000454, 0.671732096998312, 0.6679193269956158]</t>
+          <t>[0.7021027790001426, 0.7038913890000913, 0.7135879550000936, 0.7271815169997353, 0.6861508380002306, 0.7138318090001121, 0.706231488999947, 0.6989679110001816, 0.7075003649997598, 0.6797443229997953]</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>[1.28515625, 1.28515625, 1.28515625, 1.28515625, 1.28515625, 1.28515625, 1.28515625, 1.28515625, 1.28515625, 1.28515625]</t>
+          <t>[2.57421875, 4.37890625, 2.31640625, 2.31640625, 2.31640625, 2.31640625, 2.31640625, 2.31640625, 2.31640625, 2.31640625]</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>[148651.50018537574, 150453.20718775253, 149150.0493536871, 141445.2393083667, 145945.74448585729, 146909.24356169082, 148181.4046656023, 145901.20602723802, 148868.87264559473, 149718.6800235478]</t>
+          <t>[142429.28954420175, 142067.37227181369, 140136.89454719968, 137517.24660520544, 145740.5492521841, 140089.02200656108, 141596.6316393002, 143068.084280015, 141342.68326495343, 147114.13779623448]</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -1324,35 +1324,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-06-25T06:39:20.795399</t>
+          <t>2025-06-29T21:32:11.936524</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.8049381130993425</v>
+        <v>0.8228220055000748</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01783837122805005</v>
+        <v>0.02034976296448907</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7856258259998867</v>
+        <v>0.7923847860001842</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8354895779993967</v>
+        <v>0.8524907999999414</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7960413754990441</v>
+        <v>0.8232278159998714</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7909815362490917</v>
+        <v>0.8066717545002575</v>
       </c>
       <c r="K9" t="n">
-        <v>0.819535676500891</v>
+        <v>0.8387033682499805</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7921773110497732</v>
+        <v>0.8082646620282018</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8176989151489118</v>
+        <v>0.8373793489719478</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1367,20 +1367,20 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>124287.4826278376</v>
+        <v>121600.0058892416</v>
       </c>
       <c r="S9" t="n">
-        <v>2724.208963191619</v>
+        <v>3012.315990646543</v>
       </c>
       <c r="T9" t="n">
-        <v>119690.3021093965</v>
+        <v>117303.3186985794</v>
       </c>
       <c r="U9" t="n">
-        <v>127287.0578977306</v>
+        <v>126201.3125022024</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>[0.8157998349997797, 0.793910833002883, 0.8354895779993967, 0.8207809570012614, 0.7976964659974328, 0.826054134995502, 0.790005103997828, 0.7896321119987988, 0.7943862850006553, 0.7856258259998867]</t>
+          <t>[0.8046036650002861, 0.8018237240003145, 0.8128760230001717, 0.812883771000088, 0.7923847860001842, 0.8524907999999414, 0.8350030609999521, 0.8335718609996547, 0.8399368039999899, 0.8426455600001646]</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>[122579.08828827724, 125958.72967466721, 119690.30210939652, 121835.18531588728, 125360.96656133591, 121057.44135103752, 126581.46066898694, 126641.25290810376, 125883.34150295345, 127287.05789773058]</t>
+          <t>[124284.79306015147, 124715.6912508126, 123019.98972846918, 123018.81716370146, 126201.31250220237, 117303.31869857936, 119760.0400173931, 119965.66184476975, 119056.57607069353, 118673.85855564286]</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="AC9" t="n">
-        <v>0.8423752827252724</v>
+        <v>0.8554936946201361</v>
       </c>
     </row>
   </sheetData>

--- a/data/resultados_experimento.xlsx
+++ b/data/resultados_experimento.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,84 +578,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Merge Sort</t>
+          <t>Merge Sort (Implementação Clássica)</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>10000</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-06-29T21:31:27.695655</t>
+          <t>2025-06-30T20:02:50.665783</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0642716523001127</v>
+        <v>0.04210308000110672</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002986806940023528</v>
+        <v>0.02730769867475834</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05936170800032414</v>
+        <v>0.02785829999993439</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06844271099998878</v>
+        <v>0.0908372000012605</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06470139950010889</v>
+        <v>0.03130950000195298</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06296408149989929</v>
+        <v>0.02829720000227098</v>
       </c>
       <c r="K2" t="n">
-        <v>0.06580232025009991</v>
+        <v>0.03221320000011474</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06213501932871297</v>
+        <v>0.008196093682862587</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06640828527151243</v>
+        <v>0.07601006631935085</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.00234375</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.003493856214843421</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.0078125</v>
       </c>
       <c r="R2" t="n">
-        <v>155896.6117900158</v>
+        <v>290452.3973020904</v>
       </c>
       <c r="S2" t="n">
-        <v>7348.646558730344</v>
+        <v>102984.1194367339</v>
       </c>
       <c r="T2" t="n">
-        <v>146107.5964685508</v>
+        <v>110087.0568430251</v>
       </c>
       <c r="U2" t="n">
-        <v>168458.7646963493</v>
+        <v>358959.4483519652</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>[0.06287675299972761, 0.06603549300007217, 0.06510280200018315, 0.06322606700041433, 0.06844271099998878, 0.06452724300015689, 0.068101150000075, 0.06016704000012396, 0.0648755560000609, 0.05936170800032414]</t>
+          <t>[0.028297200002270984, 0.03130950000195298, 0.0908372000012605, 0.02785829999993439, 0.03221320000011474]</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
+          <t>[0.0078125, 0.00390625, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>[159041.29146177953, 151433.71459328805, 153603.21971966533, 158162.61352986685, 146107.59646855076, 154973.30329107176, 146840.3984365754, 166203.95485600416, 154141.26084700704, 168458.7646963493]</t>
+          <t>[353391.85499616404, 319391.8778446233, 110087.05684302506, 358959.44835196517, 310431.7484746744]</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -668,7 +668,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>merge_sort</t>
+          <t>merge_sort_implementação_clássica</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -683,46 +683,46 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Quick Sort</t>
+          <t>Merge Sort (Híbrido com Insertion Sort, cutoff=10)</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>10000</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-06-29T21:31:29.215455</t>
+          <t>2025-06-30T20:02:51.090380</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.05179314290003276</v>
+        <v>0.02171305999945616</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006735991211896062</v>
+        <v>0.001487619307373979</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04704201300000932</v>
+        <v>0.02046390000032261</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06835226499970304</v>
+        <v>0.02400510000006761</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04897329549999085</v>
+        <v>0.02105159999700845</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04739303075018597</v>
+        <v>0.02064830000017537</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05445494474997759</v>
+        <v>0.02239639999970677</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04697450506792615</v>
+        <v>0.01986593666245707</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05661178073213938</v>
+        <v>0.02356018333645525</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -737,30 +737,30 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>195585.1689254989</v>
+        <v>462213.7054778684</v>
       </c>
       <c r="S3" t="n">
-        <v>21577.58799858037</v>
+        <v>30336.27025843985</v>
       </c>
       <c r="T3" t="n">
-        <v>146300.9309207741</v>
+        <v>416578.1438099334</v>
       </c>
       <c r="U3" t="n">
-        <v>212575.9371733947</v>
+        <v>488665.4059022157</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>[0.04704201300000932, 0.047657956999955786, 0.04712196300033611, 0.0473047220002627, 0.0479407729999366, 0.05075450699996509, 0.05000581800004511, 0.05568842399998175, 0.06835226499970304, 0.056062987000132125]</t>
+          <t>[0.024005100000067614, 0.02046390000032261, 0.020648300000175368, 0.022396399999706773, 0.021051599997008452]</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>[212575.93717339475, 209828.54972170288, 212215.26785564245, 211395.38670039043, 208590.71254468977, 197026.8374394195, 199976.73070743447, 179570.5333662033, 146300.93092077412, 178370.802825337]</t>
+          <t>[416578.14380993345, 488665.4059022157, 484301.37105306826, 446500.3304160904, 475023.2762080343]</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -773,7 +773,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>quick_sort</t>
+          <t>merge_sort_híbrido_com_insertion_sort,_cutoff_10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -782,52 +782,52 @@
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>1.240929758291846</v>
+        <v>1.939067086912727</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Merge Sort</t>
+          <t>Merge Sort (Otimizado com Cutoff)</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>10000</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-06-29T21:31:30.827376</t>
+          <t>2025-06-30T20:02:51.531160</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.059959496700003</v>
+        <v>0.02746790000019246</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00661040440914978</v>
+        <v>0.000626215381527436</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05535168899996279</v>
+        <v>0.0267375000003085</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07585036599994055</v>
+        <v>0.02823290000014822</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05655928400005905</v>
+        <v>0.02743489999920712</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05560156425008245</v>
+        <v>0.02699340000253869</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06130843375001405</v>
+        <v>0.02794079999875976</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05523069825454193</v>
+        <v>0.0266903509058284</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06468829514546406</v>
+        <v>0.02824544909455651</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -842,30 +842,30 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>168379.1153065919</v>
+        <v>364212.5927955868</v>
       </c>
       <c r="S4" t="n">
-        <v>16195.69289689577</v>
+        <v>8294.845713675404</v>
       </c>
       <c r="T4" t="n">
-        <v>131838.5200673631</v>
+        <v>354196.6995932937</v>
       </c>
       <c r="U4" t="n">
-        <v>180662.9604384199</v>
+        <v>374006.5451102242</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>[0.06588900199994896, 0.07585036599994055, 0.061285035999844695, 0.0613162330000705, 0.05704139799991026, 0.05535168899996279, 0.05607717000020784, 0.05556135799997719, 0.05550053199976901, 0.05572218300039822]</t>
+          <t>[0.02823290000014822, 0.02743489999920712, 0.026993400002538692, 0.0267375000003085, 0.027940799998759758]</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>[151770.39712952013, 131838.52006736313, 163171.96909250965, 163088.94905511403, 175311.27129836005, 180662.96043841992, 178325.68940199615, 179981.20204340768, 180178.45306494753, 179461.74147428028]</t>
+          <t>[354196.69959329366, 364499.2327396493, 370460.9274511367, 374006.54511022416, 357899.55908362975]</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -873,104 +873,104 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>quase</t>
+          <t>exponencial</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>merge_sort</t>
+          <t>merge_sort_otimizado_com_cutoff</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10000_quase_ordenado</t>
+          <t>10000_exponencial</t>
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>1.532810298596242</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Quick Sort</t>
+          <t>Quick Sort (Implementação Clássica)</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>10000</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-06-29T21:31:32.306718</t>
+          <t>2025-06-30T20:02:51.942126</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05541215320008632</v>
+        <v>0.01951687999971909</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0008975726045036777</v>
+        <v>0.001590845328228496</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0548527680002735</v>
+        <v>0.01787599999806844</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05792404800013173</v>
+        <v>0.02186330000040471</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05517874600013783</v>
+        <v>0.01938859999791021</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05503808524974829</v>
+        <v>0.01829500000167172</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0552928245002704</v>
+        <v>0.0201615000005404</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05477006843882867</v>
+        <v>0.01754158462894712</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05605423796134397</v>
+        <v>0.02149217537049107</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.00078125</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.001746928107421711</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.00390625</v>
       </c>
       <c r="R5" t="n">
-        <v>180506.877359197</v>
+        <v>515031.2055439972</v>
       </c>
       <c r="S5" t="n">
-        <v>2816.038377731491</v>
+        <v>40778.55029322921</v>
       </c>
       <c r="T5" t="n">
-        <v>172639.8679867342</v>
+        <v>457387.4941026694</v>
       </c>
       <c r="U5" t="n">
-        <v>182306.2055856532</v>
+        <v>559409.2638778549</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>[0.054921275000197056, 0.0548527680002735, 0.055197532999955, 0.055300392000390275, 0.05515995900032067, 0.05500521599969943, 0.057924048000131734, 0.05527012199991077, 0.055136692999894876, 0.055353526000089914]</t>
+          <t>[0.017875999998068437, 0.019388599997910205, 0.018295000001671724, 0.0201615000005404, 0.021863300000404706]</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
+          <t>[0.00390625, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>[182078.80279480256, 182306.2055856532, 181167.51703392528, 180830.54456339887, 181290.92517893034, 181800.94047907463, 172639.86798673423, 180929.58072385192, 181367.4244122524, 180656.96483334695]</t>
+          <t>[559409.2638778549, 515766.99715698126, 546597.4309421284, 495994.8416403524, 457387.4941026694]</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -978,108 +978,108 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>quase</t>
+          <t>exponencial</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>quick_sort</t>
+          <t>quick_sort_implementação_clássica</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10000_quase_ordenado</t>
+          <t>10000_exponencial</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>1.082064010100759</v>
+        <v>2.157264890787499</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Merge Sort</t>
+          <t>Quick Sort (Otimizado com Median-of-Three)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-06-29T21:31:40.955936</t>
+          <t>2025-06-30T20:02:52.444094</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7424729585999558</v>
+        <v>0.02876808000073652</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02113974497291606</v>
+        <v>0.004429962113316743</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7046222049998505</v>
+        <v>0.02287190000060946</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7689441210000041</v>
+        <v>0.03295380000054138</v>
       </c>
       <c r="I6" t="n">
-        <v>0.74634063350004</v>
+        <v>0.02965580000090995</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7411172144998091</v>
+        <v>0.02563780000127736</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7519812880001382</v>
+        <v>0.03272110000034445</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7273504960427479</v>
+        <v>0.02326755553122444</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7575954211571636</v>
+        <v>0.03426860447024859</v>
       </c>
       <c r="N6" t="n">
-        <v>3.285546875</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1964070890495204</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.7265625</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.34765625</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>134785.6581354807</v>
+        <v>354707.458689097</v>
       </c>
       <c r="S6" t="n">
-        <v>3927.93679459333</v>
+        <v>57880.16646824711</v>
       </c>
       <c r="T6" t="n">
-        <v>130048.4616098645</v>
+        <v>303455.140221635</v>
       </c>
       <c r="U6" t="n">
-        <v>141920.0236529889</v>
+        <v>437217.7212970298</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>[0.7077368860000206, 0.7046222049998505, 0.7469167160002144, 0.7641639669996039, 0.7517529910001031, 0.7408490479997454, 0.7689441210000041, 0.7520573870001499, 0.7419217140000001, 0.7457645509998656]</t>
+          <t>[0.025637800001277355, 0.02965580000090995, 0.03272110000034445, 0.03295380000054138, 0.022871900000609457]</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>[2.7265625, 3.34765625, 3.34765625, 3.34765625, 3.34765625, 3.34765625, 3.34765625, 3.34765625, 3.34765625, 3.34765625]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>[141295.44747226455, 141920.02365298892, 133883.73543908112, 130861.96721972869, 133022.41719978245, 134980.2638877581, 130048.46160986446, 132968.5762397545, 134785.11022525484, 134090.57840832934]</t>
+          <t>[390049.0681533427, 337202.166176369, 305613.197597108, 303455.140221635, 437217.72129702976]</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1088,103 +1088,103 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>merge_sort</t>
+          <t>quick_sort_otimizado_com_median_of_three</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>100000_exponencial</t>
+          <t>10000_exponencial</t>
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>1.463534584165116</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Quick Sort</t>
+          <t>Quick Sort (Híbrido com Insertion Sort, cutoff=10)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-06-29T21:31:54.335485</t>
+          <t>2025-06-30T20:02:52.875483</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.210067964900009</v>
+        <v>0.0207416999990528</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0603754622000333</v>
+        <v>0.00259938360875437</v>
       </c>
       <c r="G7" t="n">
-        <v>1.146663179999905</v>
+        <v>0.01874959999986459</v>
       </c>
       <c r="H7" t="n">
-        <v>1.33491241999991</v>
+        <v>0.02467429999887827</v>
       </c>
       <c r="I7" t="n">
-        <v>1.196193957499872</v>
+        <v>0.01929939999899943</v>
       </c>
       <c r="J7" t="n">
-        <v>1.16844721450002</v>
+        <v>0.01885109999784618</v>
       </c>
       <c r="K7" t="n">
-        <v>1.225062132000176</v>
+        <v>0.02213409999967553</v>
       </c>
       <c r="L7" t="n">
-        <v>1.166877961062977</v>
+        <v>0.01751413895454151</v>
       </c>
       <c r="M7" t="n">
-        <v>1.25325796873704</v>
+        <v>0.02396926104356408</v>
       </c>
       <c r="N7" t="n">
-        <v>0.063671875</v>
+        <v>0.00078125</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2013481478935335</v>
+        <v>0.001746928107421711</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.63671875</v>
+        <v>0.00390625</v>
       </c>
       <c r="R7" t="n">
-        <v>82817.52601386004</v>
+        <v>487808.0249588654</v>
       </c>
       <c r="S7" t="n">
-        <v>3957.581777393328</v>
+        <v>56838.8919348774</v>
       </c>
       <c r="T7" t="n">
-        <v>74911.28144571969</v>
+        <v>405279.987697913</v>
       </c>
       <c r="U7" t="n">
-        <v>87209.56750351771</v>
+        <v>533344.7113576941</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>[1.154461855000136, 1.2284966760003044, 1.3349124199999096, 1.2884339110000838, 1.1999294229999578, 1.214758499999789, 1.1739533590002793, 1.1666118329999335, 1.192458491999787, 1.146663179999905]</t>
+          <t>[0.019299399998999434, 0.02467429999887827, 0.022134099999675527, 0.018749599999864586, 0.018851099997846177]</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>[0.63671875, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.00390625]</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>[86620.44533293672, 81400.30164800806, 74911.2814457197, 77613.604505628, 83338.23480216763, 82320.8892961172, 85182.25978343676, 85718.31449956303, 83860.36132150574, 87209.56750351771]</t>
+          <t>[518150.8233685215, 405279.987697913, 451791.57951516414, 533344.7113576941, 530473.0228550347]</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1193,103 +1193,103 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>quick_sort</t>
+          <t>quick_sort_híbrido_com_insertion_sort,_cutoff_10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>100000_exponencial</t>
+          <t>10000_exponencial</t>
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>0.6135795510141518</v>
+        <v>2.029876046950319</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Merge Sort</t>
+          <t>Merge Sort (Implementação Clássica)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-06-29T21:32:02.537335</t>
+          <t>2025-06-30T20:02:53.446993</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7039190375000089</v>
+        <v>0.03337553999954253</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01365855955939503</v>
+        <v>0.003305481357232058</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6797443229997953</v>
+        <v>0.02874199999860139</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7271815169997353</v>
+        <v>0.03744010000082199</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7050614390000192</v>
+        <v>0.03390460000082385</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6997516280001719</v>
+        <v>0.03174719999879017</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7120660575000102</v>
+        <v>0.03504379999867524</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6941482925933427</v>
+        <v>0.02927124280153376</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7136897824066752</v>
+        <v>0.0374798371975513</v>
       </c>
       <c r="N8" t="n">
-        <v>2.5484375</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6482445119440851</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.31640625</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.37890625</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>142110.1911207669</v>
+        <v>302061.4045395129</v>
       </c>
       <c r="S8" t="n">
-        <v>2772.226822203612</v>
+        <v>30914.49224531089</v>
       </c>
       <c r="T8" t="n">
-        <v>137517.2466052054</v>
+        <v>267093.3036979189</v>
       </c>
       <c r="U8" t="n">
-        <v>147114.1377962345</v>
+        <v>347922.9003022271</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>[0.7021027790001426, 0.7038913890000913, 0.7135879550000936, 0.7271815169997353, 0.6861508380002306, 0.7138318090001121, 0.706231488999947, 0.6989679110001816, 0.7075003649997598, 0.6797443229997953]</t>
+          <t>[0.03504379999867524, 0.031747199998790165, 0.037440100000821985, 0.03390460000082385, 0.028741999998601386]</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>[2.57421875, 4.37890625, 2.31640625, 2.31640625, 2.31640625, 2.31640625, 2.31640625, 2.31640625, 2.31640625, 2.31640625]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>[142429.28954420175, 142067.37227181369, 140136.89454719968, 137517.24660520544, 145740.5492521841, 140089.02200656108, 141596.6316393002, 143068.084280015, 141342.68326495343, 147114.13779623448]</t>
+          <t>[285357.1815949763, 314988.4084385736, 267093.3036979189, 294945.2286638689, 347922.90030222706]</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>merge_sort</t>
+          <t>merge_sort_implementação_clássica</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>100000_quase_ordenado</t>
+          <t>10000_quase_ordenado</t>
         </is>
       </c>
       <c r="AC8" t="n">
@@ -1313,106 +1313,1786 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Quick Sort</t>
+          <t>Merge Sort (Híbrido com Insertion Sort, cutoff=10)</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:02:53.932656</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02377683999948204</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.002807048789294668</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02083789999960572</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02785489999951096</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02266880000024685</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02217670000027283</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02534589999777381</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02029142857661338</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0272622514223507</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>425099.5737233801</v>
+      </c>
+      <c r="S9" t="n">
+        <v>48034.04556266969</v>
+      </c>
+      <c r="T9" t="n">
+        <v>359003.2633459666</v>
+      </c>
+      <c r="U9" t="n">
+        <v>479894.807067373</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>[0.022668800000246847, 0.025345899997773813, 0.02217670000027283, 0.020837899999605725, 0.027854899999510963]</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[441134.95199971355, 394541.12897463975, 450923.71722920786, 479894.80706737295, 359003.26334596664]</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>quase</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>merge_sort_híbrido_com_insertion_sort,_cutoff_10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10000_quase_ordenado</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.403699566480222</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Merge Sort (Otimizado com Cutoff)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:02:54.467893</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.03076020000080461</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.007021787819884344</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.02439030000095954</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.04004290000011679</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.02705880000212346</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.02584099999876344</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.03646800000205985</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.02204149886182851</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.03947890113978072</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>338098.3389154114</v>
+      </c>
+      <c r="S10" t="n">
+        <v>71483.24943940844</v>
+      </c>
+      <c r="T10" t="n">
+        <v>249732.1622552521</v>
+      </c>
+      <c r="U10" t="n">
+        <v>409999.0569860391</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>[0.04004290000011679, 0.03646800000205985, 0.02439030000095954, 0.027058800002123462, 0.025840999998763436]</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[249732.1622552521, 274213.00864964246, 409999.0569860391, 369565.53872364043, 386981.9279624832]</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>quase</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>merge_sort_otimizado_com_cutoff</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10000_quase_ordenado</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.085023504355287</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Quick Sort (Implementação Clássica)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:02:54.938369</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.03331114000029629</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0009935417978236909</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0327158000000054</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.03508140000121784</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.03292209999926854</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.03291130000070552</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.03292510000028415</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.03207749491922797</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.03454478508136462</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>300405.6074869449</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8622.411954405306</v>
+      </c>
+      <c r="T11" t="n">
+        <v>285051.3377360326</v>
+      </c>
+      <c r="U11" t="n">
+        <v>305662.7073156807</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>[0.03291130000070552, 0.03292209999926854, 0.035081400001217844, 0.032925100000284147, 0.0327158000000054]</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>[303847.0069485444, 303747.3308270791, 285051.33773603255, 303719.65460738767, 305662.70731568075]</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>quase</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>quick_sort_implementação_clássica</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10000_quase_ordenado</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.001933287159961</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Quick Sort (Otimizado com Median-of-Three)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:02:55.584671</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.04278231999996933</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.004584040988556777</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.03514190000350936</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.0464654999996128</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.04311509999752161</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.04294640000080108</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0462426999984018</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.03709048133818797</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.04847415866175069</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>236162.0145685498</v>
+      </c>
+      <c r="S12" t="n">
+        <v>28313.28430047533</v>
+      </c>
+      <c r="T12" t="n">
+        <v>215213.4379288575</v>
+      </c>
+      <c r="U12" t="n">
+        <v>284560.5957276463</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>[0.03514190000350936, 0.046242699998401804, 0.0464654999996128, 0.04311509999752161, 0.04294640000080108]</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>[284560.5957276463, 216250.34871116112, 215213.43792885754, 231937.30272166437, 232848.38775341987]</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>quase</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>quick_sort_otimizado_com_median_of_three</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10000_quase_ordenado</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.7801245935135461</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Quick Sort (Híbrido com Insertion Sort, cutoff=10)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:02:56.106892</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.03336490000001504</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.002635990166567301</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.03133950000119512</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.03797649999978603</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.03248030000031576</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.03220230000079027</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.03282589999798802</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.03009188591056927</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.03663791408946081</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>301092.0252869672</v>
+      </c>
+      <c r="S13" t="n">
+        <v>21784.71312221535</v>
+      </c>
+      <c r="T13" t="n">
+        <v>263320.737826191</v>
+      </c>
+      <c r="U13" t="n">
+        <v>319086.1372905967</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>[0.032480300000315765, 0.032202300000790274, 0.03133950000119512, 0.03282589999798802, 0.03797649999978603]</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>[307878.9296866957, 310536.8250017729, 319086.1372905967, 304637.49662957987, 263320.737826191]</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>quase</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>quick_sort_híbrido_com_insertion_sort,_cutoff_10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10000_quase_ordenado</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000318897989428</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Merge Sort (Implementação Clássica)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>100000</v>
       </c>
-      <c r="C9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025-06-29T21:32:11.936524</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.8228220055000748</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.02034976296448907</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.7923847860001842</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.8524907999999414</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.8232278159998714</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.8066717545002575</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.8387033682499805</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.8082646620282018</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.8373793489719478</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>121600.0058892416</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3012.315990646543</v>
-      </c>
-      <c r="T9" t="n">
-        <v>117303.3186985794</v>
-      </c>
-      <c r="U9" t="n">
-        <v>126201.3125022024</v>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>[0.8046036650002861, 0.8018237240003145, 0.8128760230001717, 0.812883771000088, 0.7923847860001842, 0.8524907999999414, 0.8350030609999521, 0.8335718609996547, 0.8399368039999899, 0.8426455600001646]</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>[124284.79306015147, 124715.6912508126, 123019.98972846918, 123018.81716370146, 126201.31250220237, 117303.31869857936, 119760.0400173931, 119965.66184476975, 119056.57607069353, 118673.85855564286]</t>
-        </is>
-      </c>
-      <c r="Y9" t="n">
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:02:58.921376</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4571966800009249</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.06707650540024433</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.3947549000004074</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5680924000007508</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.4371409000013955</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4206959000002826</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.4652993000017887</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3739101981201211</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.5404831618817288</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.4984375</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.2480637912538829</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.0546875</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.609375</v>
+      </c>
+      <c r="R14" t="n">
+        <v>222145.0925485079</v>
+      </c>
+      <c r="S14" t="n">
+        <v>29312.15622667061</v>
+      </c>
+      <c r="T14" t="n">
+        <v>176027.7025354816</v>
+      </c>
+      <c r="U14" t="n">
+        <v>253321.7447076573</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>[0.5680924000007508, 0.39475490000040736, 0.4371409000013955, 0.42069590000028256, 0.46529930000178865]</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>[2.0546875, 2.609375, 2.609375, 2.609375, 2.609375]</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>[176027.70253548163, 253321.74470765734, 228759.19411723033, 237701.38953085314, 214915.43185131717]</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
         <v>100000</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>exponencial</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>merge_sort_implementação_clássica</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>100000_exponencial</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Merge Sort (Híbrido com Insertion Sort, cutoff=10)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:03:01.337621</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.3807534999999916</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.02868266577553567</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.3413154999980179</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4030576000004658</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.3987686000000394</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.3589468000027409</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.4016789999986941</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3451392665339977</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.4163677334659856</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.609375</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.609375</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.609375</v>
+      </c>
+      <c r="R15" t="n">
+        <v>263881.4767258627</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20657.84396281685</v>
+      </c>
+      <c r="T15" t="n">
+        <v>248103.4968696396</v>
+      </c>
+      <c r="U15" t="n">
+        <v>292984.0572742249</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>[0.3413154999980179, 0.35894680000274093, 0.39876860000003944, 0.40167899999869405, 0.40305760000046575]</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>[2.609375, 2.609375, 2.609375, 2.609375, 2.609375]</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>[292984.05727422494, 278592.8165378167, 250772.0016069222, 248955.01134071016, 248103.49686963958]</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>exponencial</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>merge_sort_híbrido_com_insertion_sort,_cutoff_10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>100000_exponencial</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.200768161030522</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Merge Sort (Otimizado com Cutoff)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:03:04.064018</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.4578362600004766</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.02561050387345909</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.4212800999994215</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4910491999980877</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4622305000011693</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.4482477000019571</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.4663738000017474</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4260366193649444</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.4896359006360089</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.609375</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.609375</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.609375</v>
+      </c>
+      <c r="R16" t="n">
+        <v>218974.1681453194</v>
+      </c>
+      <c r="S16" t="n">
+        <v>12430.3016871165</v>
+      </c>
+      <c r="T16" t="n">
+        <v>203645.5817469806</v>
+      </c>
+      <c r="U16" t="n">
+        <v>237371.7628725813</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>[0.4910491999980877, 0.44824770000195713, 0.4212800999994215, 0.46637380000174744, 0.4622305000011693]</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>[2.609375, 2.609375, 2.609375, 2.609375, 2.609375]</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>[203645.5817469806, 223090.93833512894, 237371.76287258125, 214420.27832529467, 216342.27944661168]</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>exponencial</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>merge_sort_otimizado_com_cutoff</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>100000_exponencial</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.9986030376896077</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Quick Sort (Implementação Clássica)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:03:07.298743</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5681457399994543</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.03620109687642589</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.5265614999989339</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6070650000001478</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5768917999994301</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5342577000010351</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.5959526999977243</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.5231961413125095</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.6130953386863991</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.153125</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.3423979090546553</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.765625</v>
+      </c>
+      <c r="R17" t="n">
+        <v>176591.0436573956</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11380.66056550847</v>
+      </c>
+      <c r="T17" t="n">
+        <v>164727.0061689863</v>
+      </c>
+      <c r="U17" t="n">
+        <v>189911.3398913564</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>[0.5342577000010351, 0.5265614999989339, 0.6070650000001478, 0.5959526999977243, 0.5768917999994301]</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>[0.765625, 0.0, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>[187175.58960742402, 189911.33989135642, 164727.00616898626, 167798.5517984596, 173342.73082075146]</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>exponencial</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>quick_sort_implementação_clássica</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>100000_exponencial</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.8047172544167349</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Quick Sort (Otimizado com Median-of-Three)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:03:11.177514</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.68846840000042</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.08132909592294471</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.5898245999997016</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.7830830000020796</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7153940999996848</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.6187619000011182</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.7352783999995154</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.5874849895864388</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.7894518104144012</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>146928.2732161313</v>
+      </c>
+      <c r="S18" t="n">
+        <v>17798.51889853442</v>
+      </c>
+      <c r="T18" t="n">
+        <v>127700.3842501171</v>
+      </c>
+      <c r="U18" t="n">
+        <v>169541.9282275622</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>[0.6187619000011182, 0.7352783999995154, 0.7153940999996848, 0.7830830000020796, 0.5898245999997016]</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>[161613.0534213876, 136002.9071982339, 139783.0929833557, 127700.38425011707, 169541.92822756222]</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>exponencial</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>quick_sort_otimizado_com_median_of_three</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>100000_exponencial</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.6640779446095798</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Quick Sort (Híbrido com Insertion Sort, cutoff=10)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:03:14.816354</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6420134200001485</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0189238616586051</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6164825999985624</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.667037999999593</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6408852000022307</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6341189000013401</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.6515423999990162</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.61851634227167</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.665510497728627</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>155868.4692708112</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4602.243833381151</v>
+      </c>
+      <c r="T19" t="n">
+        <v>149916.4965115346</v>
+      </c>
+      <c r="U19" t="n">
+        <v>162210.5798285843</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>[0.6164825999985624, 0.667037999999593, 0.6408852000022307, 0.6341189000013401, 0.6515423999990162]</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>[162210.5798285843, 149916.49651153458, 156034.18521702784, 157699.13181863632, 153481.95297827278]</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>exponencial</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>quick_sort_híbrido_com_insertion_sort,_cutoff_10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>100000_exponencial</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.7121294754256371</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Merge Sort (Implementação Clássica)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:03:16.846416</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.33135881999915</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.01163381685779316</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.3180702999998175</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3436180999997305</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.3271322999971744</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.3244254999990517</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.3435478999999759</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.3169135284451322</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.3458041115531679</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.45625</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.3423979090546553</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.84375</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.609375</v>
+      </c>
+      <c r="R20" t="n">
+        <v>302084.1571009852</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10558.20269168322</v>
+      </c>
+      <c r="T20" t="n">
+        <v>291020.7582198913</v>
+      </c>
+      <c r="U20" t="n">
+        <v>314395.9055594231</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>[0.3271322999971744, 0.3435478999999759, 0.3244254999990517, 0.3436180999997305, 0.3180702999998175]</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>[1.84375, 2.609375, 2.609375, 2.609375, 2.609375]</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>[305686.72063524066, 291080.2249118886, 308237.1761784826, 291020.75821989134, 314395.9055594231]</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>quase</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>quick_sort</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>merge_sort_implementação_clássica</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>100000_quase_ordenado</t>
         </is>
       </c>
-      <c r="AC9" t="n">
-        <v>0.8554936946201361</v>
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Merge Sort (Híbrido com Insertion Sort, cutoff=10)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:03:18.659038</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.2871657600000617</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.0452444745708979</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.2595308999989356</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3661860000029264</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2644512999977451</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.2615740000001097</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.2840866000005917</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.230987324807732</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.3433441951923915</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.609375</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.609375</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.609375</v>
+      </c>
+      <c r="R21" t="n">
+        <v>354168.7252702021</v>
+      </c>
+      <c r="S21" t="n">
+        <v>47210.00757930903</v>
+      </c>
+      <c r="T21" t="n">
+        <v>273085.2626785318</v>
+      </c>
+      <c r="U21" t="n">
+        <v>385310.5738099398</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>[0.2840866000005917, 0.2644512999977451, 0.26157400000010966, 0.25953089999893564, 0.36618600000292645]</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>[2.609375, 2.609375, 2.609375, 2.609375, 2.609375]</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>[352005.3392162521, 378141.4574284667, 382300.9932178201, 385310.57380993984, 273085.26267853176]</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>quase</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>merge_sort_híbrido_com_insertion_sort,_cutoff_10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>100000_quase_ordenado</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.153893904339705</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Merge Sort (Otimizado com Cutoff)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:03:20.774650</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.347483720001037</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.0302938875266055</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.3180637000004936</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.3875326000015775</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.3375694000023941</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3236437000014121</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.3706091999993077</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.3098688904936168</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.3850985495084572</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.609375</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.609375</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.609375</v>
+      </c>
+      <c r="R22" t="n">
+        <v>289497.6766972611</v>
+      </c>
+      <c r="S22" t="n">
+        <v>24605.16377642345</v>
+      </c>
+      <c r="T22" t="n">
+        <v>258042.8072363278</v>
+      </c>
+      <c r="U22" t="n">
+        <v>314402.429449965</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>[0.3375694000023941, 0.3875326000015775, 0.32364370000141207, 0.31806370000049355, 0.37060919999930775]</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>[2.609375, 2.609375, 2.609375, 2.609375, 2.609375]</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>[296235.38152240927, 258042.80723632782, 308981.7598784209, 314402.42944996495, 269826.00539918273]</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>quase</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>merge_sort_otimizado_com_cutoff</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>100000_quase_ordenado</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.9535952360535369</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Quick Sort (Implementação Clássica)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:03:24.250359</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6128532599999744</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.03565419847680056</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.5706820000013977</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.6577601999997569</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6123178999987431</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.5863845000021684</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.637121699997806</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.5685827253665197</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.6571237946334292</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.153125</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.3423979090546553</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.765625</v>
+      </c>
+      <c r="R23" t="n">
+        <v>163613.2677969282</v>
+      </c>
+      <c r="S23" t="n">
+        <v>9505.433820086459</v>
+      </c>
+      <c r="T23" t="n">
+        <v>152031.0897497857</v>
+      </c>
+      <c r="U23" t="n">
+        <v>175228.9366052462</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>[0.6123178999987431, 0.5706820000013977, 0.637121699997806, 0.5863845000021684, 0.6577601999997569]</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>[0.765625, 0.0, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>[163313.860333342, 175228.93660524616, 156955.88456702128, 170536.56772924628, 152031.08974978566]</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>quase</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>quick_sort_implementação_clássica</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>100000_quase_ordenado</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.5406821528519956</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Quick Sort (Otimizado com Median-of-Three)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:03:27.313134</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.534594320000906</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.01117887340880576</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.5205098999977054</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5459673000004841</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5335101000018767</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5274430000026769</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.545541300001787</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.5207139153487145</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.5484747246530975</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>187123.2917496999</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3919.419996225176</v>
+      </c>
+      <c r="T24" t="n">
+        <v>183161.1526915831</v>
+      </c>
+      <c r="U24" t="n">
+        <v>192119.3045520188</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>[0.545541300001787, 0.5335101000018767, 0.5274430000026769, 0.5205098999977054, 0.5459673000004841]</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>[183304.17880309417, 187437.87605829438, 189593.94664350932, 192119.3045520188, 183161.15269158306]</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>quase</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>quick_sort_otimizado_com_median_of_three</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>100000_quase_ordenado</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.6198322870295151</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Quick Sort (Híbrido com Insertion Sort, cutoff=10)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-06-30T20:03:30.269088</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5173731600007159</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.02822043729479367</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.4943935000010242</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5613086000012117</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.5030196000006981</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4982707000017399</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.5298733999989054</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.4823328589982037</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.5524134610032281</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.00078125</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.001746928107421711</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.00390625</v>
+      </c>
+      <c r="R25" t="n">
+        <v>193728.2012855156</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10182.45531320706</v>
+      </c>
+      <c r="T25" t="n">
+        <v>178155.1182358227</v>
+      </c>
+      <c r="U25" t="n">
+        <v>202268.0314360784</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>[0.5298733999989054, 0.5030196000006981, 0.5613086000012117, 0.4982707000017399, 0.4943935000010242]</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.00390625]</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>[188724.325471342, 198799.41059923155, 178155.1182358227, 200694.12068510312, 202268.03143607843]</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>quase</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>quick_sort_híbrido_com_insertion_sort,_cutoff_10</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>100000_quase_ordenado</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.6404638771726997</v>
       </c>
     </row>
   </sheetData>
